--- a/InputData/endo-learn/BCSG/BAU CO2 Sequestered Globally.xlsx
+++ b/InputData/endo-learn/BCSG/BAU CO2 Sequestered Globally.xlsx
@@ -1,37 +1,89 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28512"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipL\InputData\endo-learn\BCSG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\endo-learn\BCSG\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{8AA84856-6CF0-41A4-8A5B-B108EC39E953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{089CA91D-15E0-4BC3-A858-3F75A7BB04CB}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22635" windowHeight="13365"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Data" sheetId="2" r:id="rId2"/>
     <sheet name="BCSG" sheetId="3" r:id="rId3"/>
+    <sheet name="SYBCSG" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
   <si>
     <t>BCSG BAU CO2 Sequestered Globally</t>
   </si>
   <si>
+    <t>SYBCSG Start Year BAU CO2 Sequestered Globally</t>
+  </si>
+  <si>
     <t>Source:</t>
+  </si>
+  <si>
+    <t>International Energy Agency</t>
+  </si>
+  <si>
+    <t>Energy Technology Perspectives 2017</t>
+  </si>
+  <si>
+    <t>https://www.iea.org/etp2017/</t>
+  </si>
+  <si>
+    <t>Reference Technology Scenario (RTS)</t>
+  </si>
+  <si>
+    <t>About</t>
+  </si>
+  <si>
+    <t>The RTS assumes countries enact policies to meet their Paris pledges,</t>
+  </si>
+  <si>
+    <t>so it may not be entirely "BAU," but as an estimate of what countries</t>
+  </si>
+  <si>
+    <t>outside the modeled region are doing, it is arguably a better fit for</t>
+  </si>
+  <si>
+    <t>the EPS model than a true "BAU" (as we want for in-region variables).</t>
+  </si>
+  <si>
+    <t>In the case of CCS, deployment in the RTS is very modest, and is</t>
+  </si>
+  <si>
+    <t>in line with the current pace of deployment and some growth in</t>
+  </si>
+  <si>
+    <t>the lowest-cost applications.</t>
   </si>
   <si>
     <t>Global CCS</t>
@@ -117,53 +169,17 @@
     </r>
   </si>
   <si>
-    <t>International Energy Agency</t>
-  </si>
-  <si>
-    <t>Energy Technology Perspectives 2017</t>
-  </si>
-  <si>
-    <t>https://www.iea.org/etp2017/</t>
-  </si>
-  <si>
-    <t>Reference Technology Scenario (RTS)</t>
-  </si>
-  <si>
-    <t>About</t>
-  </si>
-  <si>
-    <t>The RTS assumes countries enact policies to meet their Paris pledges,</t>
-  </si>
-  <si>
-    <t>so it may not be entirely "BAU," but as an estimate of what countries</t>
-  </si>
-  <si>
-    <t>outside the modeled region are doing, it is arguably a better fit for</t>
-  </si>
-  <si>
-    <t>the EPS model than a true "BAU" (as we want for in-region variables).</t>
-  </si>
-  <si>
-    <t>In the case of CCS, deployment in the RTS is very modest, and is</t>
-  </si>
-  <si>
-    <t>in line with the current pace of deployment and some growth in</t>
-  </si>
-  <si>
-    <t>the lowest-cost applications.</t>
-  </si>
-  <si>
     <t>BAU Carbon Sequestered Globally (metric tons CO2e/yr)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#\ ##0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -259,7 +275,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -278,7 +294,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -843,89 +859,94 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="38.73046875" customWidth="1"/>
+    <col min="2" max="2" width="38.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A3" s="1" t="s">
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="B5" s="12">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="B7" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B4" s="12">
-        <v>2017</v>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B5" t="s">
-        <v>10</v>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B6" s="13" t="s">
-        <v>11</v>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B7" t="s">
-        <v>12</v>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A9" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1"/>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -933,25 +954,25 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A15:AN27"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1328125" customWidth="1"/>
+    <col min="1" max="1" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="13.1328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="15" spans="1:1" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="15" spans="1:1" ht="23.25">
       <c r="A15" s="2" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:40" ht="15.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:40" ht="18">
       <c r="A17" s="3" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B17" s="4">
         <v>2014</v>
@@ -1065,9 +1086,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="18" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:40">
       <c r="A18" s="5" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B18" s="6">
         <v>0</v>
@@ -1211,9 +1232,9 @@
         <v>645.25886199836145</v>
       </c>
     </row>
-    <row r="19" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:40">
       <c r="A19" s="5" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B19" s="6">
         <v>0</v>
@@ -1357,9 +1378,9 @@
         <v>140.98274447844116</v>
       </c>
     </row>
-    <row r="20" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:40">
       <c r="A20" s="7" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B20" s="8">
         <v>0</v>
@@ -1503,9 +1524,9 @@
         <v>133.61743935810051</v>
       </c>
     </row>
-    <row r="21" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:40">
       <c r="A21" s="9" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="B21" s="10">
         <v>0</v>
@@ -1649,9 +1670,9 @@
         <v>919.8590458349031</v>
       </c>
     </row>
-    <row r="23" spans="1:40" ht="15.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:40" ht="18">
       <c r="A23" s="3" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B23" s="4">
         <v>2014</v>
@@ -1765,9 +1786,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="24" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:40">
       <c r="A24" s="5" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B24" s="6">
         <v>0</v>
@@ -1913,9 +1934,9 @@
       <c r="AM24" s="5"/>
       <c r="AN24" s="5"/>
     </row>
-    <row r="25" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:40">
       <c r="A25" s="5" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B25" s="6">
         <v>0</v>
@@ -2061,9 +2082,9 @@
       <c r="AM25" s="5"/>
       <c r="AN25" s="5"/>
     </row>
-    <row r="26" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:40">
       <c r="A26" s="7" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B26" s="8">
         <v>0</v>
@@ -2209,9 +2230,9 @@
       <c r="AM26" s="5"/>
       <c r="AN26" s="5"/>
     </row>
-    <row r="27" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:40">
       <c r="A27" s="9" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="B27" s="10">
         <v>0</v>
@@ -2364,269 +2385,576 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
-    <tabColor theme="3"/>
+    <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AJ2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="43.3984375" customWidth="1"/>
+    <col min="1" max="1" width="43.42578125" customWidth="1"/>
+    <col min="32" max="32" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:51">
       <c r="B1">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="C1">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="D1">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="E1">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="F1">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="G1">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="H1">
-        <v>2022</v>
+        <v>2027</v>
       </c>
       <c r="I1">
-        <v>2023</v>
+        <v>2028</v>
       </c>
       <c r="J1">
-        <v>2024</v>
+        <v>2029</v>
       </c>
       <c r="K1">
-        <v>2025</v>
+        <v>2030</v>
       </c>
       <c r="L1">
-        <v>2026</v>
+        <v>2031</v>
       </c>
       <c r="M1">
-        <v>2027</v>
+        <v>2032</v>
       </c>
       <c r="N1">
-        <v>2028</v>
+        <v>2033</v>
       </c>
       <c r="O1">
-        <v>2029</v>
+        <v>2034</v>
       </c>
       <c r="P1">
-        <v>2030</v>
+        <v>2035</v>
       </c>
       <c r="Q1">
-        <v>2031</v>
+        <v>2036</v>
       </c>
       <c r="R1">
-        <v>2032</v>
+        <v>2037</v>
       </c>
       <c r="S1">
-        <v>2033</v>
+        <v>2038</v>
       </c>
       <c r="T1">
-        <v>2034</v>
+        <v>2039</v>
       </c>
       <c r="U1">
-        <v>2035</v>
+        <v>2040</v>
       </c>
       <c r="V1">
-        <v>2036</v>
+        <v>2041</v>
       </c>
       <c r="W1">
-        <v>2037</v>
+        <v>2042</v>
       </c>
       <c r="X1">
-        <v>2038</v>
+        <v>2043</v>
       </c>
       <c r="Y1">
-        <v>2039</v>
+        <v>2044</v>
       </c>
       <c r="Z1">
-        <v>2040</v>
+        <v>2045</v>
       </c>
       <c r="AA1">
-        <v>2041</v>
+        <v>2046</v>
       </c>
       <c r="AB1">
-        <v>2042</v>
+        <v>2047</v>
       </c>
       <c r="AC1">
-        <v>2043</v>
+        <v>2048</v>
       </c>
       <c r="AD1">
-        <v>2044</v>
+        <v>2049</v>
       </c>
       <c r="AE1">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="AF1">
-        <v>2046</v>
+        <v>2051</v>
       </c>
       <c r="AG1">
-        <v>2047</v>
+        <v>2052</v>
       </c>
       <c r="AH1">
-        <v>2048</v>
+        <v>2053</v>
       </c>
       <c r="AI1">
-        <v>2049</v>
+        <v>2054</v>
       </c>
       <c r="AJ1">
-        <v>2050</v>
+        <v>2055</v>
+      </c>
+      <c r="AK1">
+        <v>2056</v>
+      </c>
+      <c r="AL1">
+        <v>2057</v>
+      </c>
+      <c r="AM1">
+        <v>2058</v>
+      </c>
+      <c r="AN1">
+        <v>2059</v>
+      </c>
+      <c r="AO1">
+        <v>2060</v>
+      </c>
+      <c r="AP1">
+        <v>2061</v>
+      </c>
+      <c r="AQ1">
+        <v>2062</v>
+      </c>
+      <c r="AR1">
+        <v>2063</v>
+      </c>
+      <c r="AS1">
+        <v>2064</v>
+      </c>
+      <c r="AT1">
+        <v>2065</v>
+      </c>
+      <c r="AU1">
+        <v>2066</v>
+      </c>
+      <c r="AV1">
+        <v>2067</v>
+      </c>
+      <c r="AW1">
+        <v>2068</v>
+      </c>
+      <c r="AX1">
+        <v>2069</v>
+      </c>
+      <c r="AY1">
+        <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:36" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:51" ht="30">
       <c r="A2" s="14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="11">
-        <f>Data!D21*10^6</f>
-        <v>54888170.608915798</v>
-      </c>
-      <c r="C2" s="11">
-        <f>Data!E21*10^6</f>
-        <v>82332255.913373694</v>
-      </c>
-      <c r="D2" s="11">
-        <f>Data!F21*10^6</f>
-        <v>109776341.2178316</v>
-      </c>
-      <c r="E2" s="11">
-        <f>Data!G21*10^6</f>
-        <v>137220426.52228951</v>
-      </c>
-      <c r="F2" s="11">
-        <f>Data!H21*10^6</f>
-        <v>164664511.82674739</v>
-      </c>
-      <c r="G2" s="11">
         <f>Data!I21*10^6</f>
         <v>192108597.13120529</v>
       </c>
-      <c r="H2" s="11">
+      <c r="C2" s="11">
         <f>Data!J21*10^6</f>
         <v>219552682.43566319</v>
       </c>
-      <c r="I2" s="11">
+      <c r="D2" s="11">
         <f>Data!K21*10^6</f>
         <v>246996767.7401211</v>
       </c>
-      <c r="J2" s="11">
+      <c r="E2" s="11">
         <f>Data!L21*10^6</f>
         <v>274440853.04457903</v>
       </c>
-      <c r="K2" s="11">
+      <c r="F2" s="11">
         <f>Data!M21*10^6</f>
         <v>301884938.34903687</v>
       </c>
-      <c r="L2" s="11">
+      <c r="G2" s="11">
         <f>Data!N21*10^6</f>
         <v>306967130.85742247</v>
       </c>
-      <c r="M2" s="11">
+      <c r="H2" s="11">
         <f>Data!O21*10^6</f>
         <v>312049323.36580819</v>
       </c>
-      <c r="N2" s="11">
+      <c r="I2" s="11">
         <f>Data!P21*10^6</f>
         <v>317131515.87419373</v>
       </c>
-      <c r="O2" s="11">
+      <c r="J2" s="11">
         <f>Data!Q21*10^6</f>
         <v>322213708.38257939</v>
       </c>
-      <c r="P2" s="11">
+      <c r="K2" s="11">
         <f>Data!R21*10^6</f>
         <v>327295900.89096504</v>
       </c>
-      <c r="Q2" s="11">
+      <c r="L2" s="11">
         <f>Data!S21*10^6</f>
         <v>351613892.14196104</v>
       </c>
-      <c r="R2" s="11">
+      <c r="M2" s="11">
         <f>Data!T21*10^6</f>
         <v>375931883.39295703</v>
       </c>
-      <c r="S2" s="11">
+      <c r="N2" s="11">
         <f>Data!U21*10^6</f>
         <v>400249874.64395303</v>
       </c>
-      <c r="T2" s="11">
+      <c r="O2" s="11">
         <f>Data!V21*10^6</f>
         <v>424567865.89494902</v>
       </c>
-      <c r="U2" s="11">
+      <c r="P2" s="11">
         <f>Data!W21*10^6</f>
         <v>448885857.14594495</v>
       </c>
-      <c r="V2" s="11">
+      <c r="Q2" s="11">
         <f>Data!X21*10^6</f>
         <v>480205173.47676724</v>
       </c>
-      <c r="W2" s="11">
+      <c r="R2" s="11">
         <f>Data!Y21*10^6</f>
         <v>511524489.80758965</v>
       </c>
-      <c r="X2" s="11">
+      <c r="S2" s="11">
         <f>Data!Z21*10^6</f>
         <v>542843806.138412</v>
       </c>
-      <c r="Y2" s="11">
+      <c r="T2" s="11">
         <f>Data!AA21*10^6</f>
         <v>574163122.46923435</v>
       </c>
-      <c r="Z2" s="11">
+      <c r="U2" s="11">
         <f>Data!AB21*10^6</f>
         <v>605482438.80005658</v>
       </c>
-      <c r="AA2" s="11">
+      <c r="V2" s="11">
         <f>Data!AC21*10^6</f>
         <v>627999020.29315913</v>
       </c>
-      <c r="AB2" s="11">
+      <c r="W2" s="11">
         <f>Data!AD21*10^6</f>
         <v>650515601.78626168</v>
       </c>
-      <c r="AC2" s="11">
+      <c r="X2" s="11">
         <f>Data!AE21*10^6</f>
         <v>673032183.27936423</v>
       </c>
-      <c r="AD2" s="11">
+      <c r="Y2" s="11">
         <f>Data!AF21*10^6</f>
         <v>695548764.77246666</v>
       </c>
-      <c r="AE2" s="11">
+      <c r="Z2" s="11">
         <f>Data!AG21*10^6</f>
         <v>718065346.26556909</v>
       </c>
-      <c r="AF2" s="11">
+      <c r="AA2" s="11">
         <f>Data!AH21*10^6</f>
         <v>758424086.17943585</v>
       </c>
-      <c r="AG2" s="11">
+      <c r="AB2" s="11">
         <f>Data!AI21*10^6</f>
         <v>798782826.09330285</v>
       </c>
-      <c r="AH2" s="11">
+      <c r="AC2" s="11">
         <f>Data!AJ21*10^6</f>
         <v>839141566.0071696</v>
       </c>
-      <c r="AI2" s="11">
+      <c r="AD2" s="11">
         <f>Data!AK21*10^6</f>
         <v>879500305.92103636</v>
       </c>
-      <c r="AJ2" s="11">
+      <c r="AE2" s="11">
         <f>Data!AL21*10^6</f>
         <v>919859045.83490312</v>
+      </c>
+      <c r="AF2" s="11">
+        <f>AE2+AE2-AD2</f>
+        <v>960217785.74876988</v>
+      </c>
+      <c r="AG2" s="11">
+        <f t="shared" ref="AG2:AY2" si="0">AF2+AF2-AE2</f>
+        <v>1000576525.6626366</v>
+      </c>
+      <c r="AH2" s="11">
+        <f t="shared" si="0"/>
+        <v>1040935265.5765034</v>
+      </c>
+      <c r="AI2" s="11">
+        <f t="shared" si="0"/>
+        <v>1081294005.4903703</v>
+      </c>
+      <c r="AJ2" s="11">
+        <f t="shared" si="0"/>
+        <v>1121652745.4042373</v>
+      </c>
+      <c r="AK2" s="11">
+        <f t="shared" si="0"/>
+        <v>1162011485.3181043</v>
+      </c>
+      <c r="AL2" s="11">
+        <f t="shared" si="0"/>
+        <v>1202370225.2319713</v>
+      </c>
+      <c r="AM2" s="11">
+        <f t="shared" si="0"/>
+        <v>1242728965.1458383</v>
+      </c>
+      <c r="AN2" s="11">
+        <f t="shared" si="0"/>
+        <v>1283087705.0597053</v>
+      </c>
+      <c r="AO2" s="11">
+        <f t="shared" si="0"/>
+        <v>1323446444.9735723</v>
+      </c>
+      <c r="AP2" s="11">
+        <f t="shared" si="0"/>
+        <v>1363805184.8874393</v>
+      </c>
+      <c r="AQ2" s="11">
+        <f t="shared" si="0"/>
+        <v>1404163924.8013062</v>
+      </c>
+      <c r="AR2" s="11">
+        <f t="shared" si="0"/>
+        <v>1444522664.7151732</v>
+      </c>
+      <c r="AS2" s="11">
+        <f t="shared" si="0"/>
+        <v>1484881404.6290402</v>
+      </c>
+      <c r="AT2" s="11">
+        <f t="shared" si="0"/>
+        <v>1525240144.5429072</v>
+      </c>
+      <c r="AU2" s="11">
+        <f t="shared" si="0"/>
+        <v>1565598884.4567742</v>
+      </c>
+      <c r="AV2" s="11">
+        <f t="shared" si="0"/>
+        <v>1605957624.3706412</v>
+      </c>
+      <c r="AW2" s="11">
+        <f t="shared" si="0"/>
+        <v>1646316364.2845082</v>
+      </c>
+      <c r="AX2" s="11">
+        <f t="shared" si="0"/>
+        <v>1686675104.1983752</v>
+      </c>
+      <c r="AY2" s="11">
+        <f t="shared" si="0"/>
+        <v>1727033844.1122422</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E2EAEFB-C5AA-4474-B6C9-67ADB3F5550A}">
+  <sheetPr>
+    <tabColor theme="8" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="B1">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="60">
+      <c r="A2" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="11">
+        <f>Data!H21*10^6</f>
+        <v>164664511.82674739</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
+    <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="79748b23-d81a-423e-9112-21109dc864e6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F92C12C-F9CE-4844-A9FE-92E1C70F48A9}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{637D4DA2-E71D-4E86-AF4A-596D7581519B}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1913C62-2019-4FBE-955D-B322DD85E640}"/>
 </file>
--- a/InputData/endo-learn/BCSG/BAU CO2 Sequestered Globally.xlsx
+++ b/InputData/endo-learn/BCSG/BAU CO2 Sequestered Globally.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28512"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\endo-learn\BCSG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\eps-mexico\InputData\endo-learn\BCSG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{8AA84856-6CF0-41A4-8A5B-B108EC39E953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{089CA91D-15E0-4BC3-A858-3F75A7BB04CB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEAA8AE3-E695-4853-9749-A16C07DC7B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="BCSG" sheetId="3" r:id="rId3"/>
     <sheet name="SYBCSG" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,46 +44,7 @@
     <t>BCSG BAU CO2 Sequestered Globally</t>
   </si>
   <si>
-    <t>SYBCSG Start Year BAU CO2 Sequestered Globally</t>
-  </si>
-  <si>
     <t>Source:</t>
-  </si>
-  <si>
-    <t>International Energy Agency</t>
-  </si>
-  <si>
-    <t>Energy Technology Perspectives 2017</t>
-  </si>
-  <si>
-    <t>https://www.iea.org/etp2017/</t>
-  </si>
-  <si>
-    <t>Reference Technology Scenario (RTS)</t>
-  </si>
-  <si>
-    <t>About</t>
-  </si>
-  <si>
-    <t>The RTS assumes countries enact policies to meet their Paris pledges,</t>
-  </si>
-  <si>
-    <t>so it may not be entirely "BAU," but as an estimate of what countries</t>
-  </si>
-  <si>
-    <t>outside the modeled region are doing, it is arguably a better fit for</t>
-  </si>
-  <si>
-    <t>the EPS model than a true "BAU" (as we want for in-region variables).</t>
-  </si>
-  <si>
-    <t>In the case of CCS, deployment in the RTS is very modest, and is</t>
-  </si>
-  <si>
-    <t>in line with the current pace of deployment and some growth in</t>
-  </si>
-  <si>
-    <t>the lowest-cost applications.</t>
   </si>
   <si>
     <t>Global CCS</t>
@@ -169,7 +130,46 @@
     </r>
   </si>
   <si>
+    <t>International Energy Agency</t>
+  </si>
+  <si>
+    <t>Energy Technology Perspectives 2017</t>
+  </si>
+  <si>
+    <t>https://www.iea.org/etp2017/</t>
+  </si>
+  <si>
+    <t>Reference Technology Scenario (RTS)</t>
+  </si>
+  <si>
+    <t>About</t>
+  </si>
+  <si>
+    <t>The RTS assumes countries enact policies to meet their Paris pledges,</t>
+  </si>
+  <si>
+    <t>so it may not be entirely "BAU," but as an estimate of what countries</t>
+  </si>
+  <si>
+    <t>outside the modeled region are doing, it is arguably a better fit for</t>
+  </si>
+  <si>
+    <t>the EPS model than a true "BAU" (as we want for in-region variables).</t>
+  </si>
+  <si>
+    <t>In the case of CCS, deployment in the RTS is very modest, and is</t>
+  </si>
+  <si>
+    <t>in line with the current pace of deployment and some growth in</t>
+  </si>
+  <si>
+    <t>the lowest-cost applications.</t>
+  </si>
+  <si>
     <t>BAU Carbon Sequestered Globally (metric tons CO2e/yr)</t>
+  </si>
+  <si>
+    <t>SYBCSG Start Year BAU CO2 Sequestered Globally</t>
   </si>
 </sst>
 </file>
@@ -179,7 +179,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#\ ##0"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -294,7 +294,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -861,87 +861,87 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="38.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="B4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12">
         <v>2017</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="13" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -956,7 +956,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A15:AN27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.140625" customWidth="1"/>
@@ -965,14 +965,14 @@
     <col min="10" max="13" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="15" spans="1:1" ht="23.25">
+    <row r="15" spans="1:1" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:40" ht="18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:40" ht="18" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B17" s="4">
         <v>2014</v>
@@ -1086,9 +1086,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="18" spans="1:40">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B18" s="6">
         <v>0</v>
@@ -1232,9 +1232,9 @@
         <v>645.25886199836145</v>
       </c>
     </row>
-    <row r="19" spans="1:40">
+    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B19" s="6">
         <v>0</v>
@@ -1378,9 +1378,9 @@
         <v>140.98274447844116</v>
       </c>
     </row>
-    <row r="20" spans="1:40">
+    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B20" s="8">
         <v>0</v>
@@ -1524,9 +1524,9 @@
         <v>133.61743935810051</v>
       </c>
     </row>
-    <row r="21" spans="1:40">
+    <row r="21" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="B21" s="10">
         <v>0</v>
@@ -1670,9 +1670,9 @@
         <v>919.8590458349031</v>
       </c>
     </row>
-    <row r="23" spans="1:40" ht="18">
+    <row r="23" spans="1:40" ht="18" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B23" s="4">
         <v>2014</v>
@@ -1786,9 +1786,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="24" spans="1:40">
+    <row r="24" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B24" s="6">
         <v>0</v>
@@ -1934,9 +1934,9 @@
       <c r="AM24" s="5"/>
       <c r="AN24" s="5"/>
     </row>
-    <row r="25" spans="1:40">
+    <row r="25" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B25" s="6">
         <v>0</v>
@@ -2082,9 +2082,9 @@
       <c r="AM25" s="5"/>
       <c r="AN25" s="5"/>
     </row>
-    <row r="26" spans="1:40">
+    <row r="26" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B26" s="8">
         <v>0</v>
@@ -2230,9 +2230,9 @@
       <c r="AM26" s="5"/>
       <c r="AN26" s="5"/>
     </row>
-    <row r="27" spans="1:40">
+    <row r="27" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="B27" s="10">
         <v>0</v>
@@ -2389,14 +2389,14 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:AZ2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.42578125" customWidth="1"/>
-    <col min="32" max="32" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.25">
       <c r="B1">
         <v>2021</v>
       </c>
@@ -2547,10 +2547,13 @@
       <c r="AY1">
         <v>2070</v>
       </c>
-    </row>
-    <row r="2" spans="1:51" ht="30">
+      <c r="AZ1">
+        <v>2071</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="11">
         <f>Data!I21*10^6</f>
@@ -2673,84 +2676,88 @@
         <v>919859045.83490312</v>
       </c>
       <c r="AF2" s="11">
-        <f>AE2+AE2-AD2</f>
-        <v>960217785.74876988</v>
+        <f>AE2</f>
+        <v>919859045.83490312</v>
       </c>
       <c r="AG2" s="11">
-        <f t="shared" ref="AG2:AY2" si="0">AF2+AF2-AE2</f>
-        <v>1000576525.6626366</v>
+        <f t="shared" ref="AG2:AZ2" si="0">AF2</f>
+        <v>919859045.83490312</v>
       </c>
       <c r="AH2" s="11">
         <f t="shared" si="0"/>
-        <v>1040935265.5765034</v>
+        <v>919859045.83490312</v>
       </c>
       <c r="AI2" s="11">
         <f t="shared" si="0"/>
-        <v>1081294005.4903703</v>
+        <v>919859045.83490312</v>
       </c>
       <c r="AJ2" s="11">
         <f t="shared" si="0"/>
-        <v>1121652745.4042373</v>
+        <v>919859045.83490312</v>
       </c>
       <c r="AK2" s="11">
         <f t="shared" si="0"/>
-        <v>1162011485.3181043</v>
+        <v>919859045.83490312</v>
       </c>
       <c r="AL2" s="11">
         <f t="shared" si="0"/>
-        <v>1202370225.2319713</v>
+        <v>919859045.83490312</v>
       </c>
       <c r="AM2" s="11">
         <f t="shared" si="0"/>
-        <v>1242728965.1458383</v>
+        <v>919859045.83490312</v>
       </c>
       <c r="AN2" s="11">
         <f t="shared" si="0"/>
-        <v>1283087705.0597053</v>
+        <v>919859045.83490312</v>
       </c>
       <c r="AO2" s="11">
         <f t="shared" si="0"/>
-        <v>1323446444.9735723</v>
+        <v>919859045.83490312</v>
       </c>
       <c r="AP2" s="11">
         <f t="shared" si="0"/>
-        <v>1363805184.8874393</v>
+        <v>919859045.83490312</v>
       </c>
       <c r="AQ2" s="11">
         <f t="shared" si="0"/>
-        <v>1404163924.8013062</v>
+        <v>919859045.83490312</v>
       </c>
       <c r="AR2" s="11">
         <f t="shared" si="0"/>
-        <v>1444522664.7151732</v>
+        <v>919859045.83490312</v>
       </c>
       <c r="AS2" s="11">
         <f t="shared" si="0"/>
-        <v>1484881404.6290402</v>
+        <v>919859045.83490312</v>
       </c>
       <c r="AT2" s="11">
         <f t="shared" si="0"/>
-        <v>1525240144.5429072</v>
+        <v>919859045.83490312</v>
       </c>
       <c r="AU2" s="11">
         <f t="shared" si="0"/>
-        <v>1565598884.4567742</v>
+        <v>919859045.83490312</v>
       </c>
       <c r="AV2" s="11">
         <f t="shared" si="0"/>
-        <v>1605957624.3706412</v>
+        <v>919859045.83490312</v>
       </c>
       <c r="AW2" s="11">
         <f t="shared" si="0"/>
-        <v>1646316364.2845082</v>
+        <v>919859045.83490312</v>
       </c>
       <c r="AX2" s="11">
         <f t="shared" si="0"/>
-        <v>1686675104.1983752</v>
+        <v>919859045.83490312</v>
       </c>
       <c r="AY2" s="11">
         <f t="shared" si="0"/>
-        <v>1727033844.1122422</v>
+        <v>919859045.83490312</v>
+      </c>
+      <c r="AZ2" s="11">
+        <f t="shared" si="0"/>
+        <v>919859045.83490312</v>
       </c>
     </row>
   </sheetData>
@@ -2764,197 +2771,26 @@
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B1">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="60">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="11">
-        <f>Data!H21*10^6</f>
-        <v>164664511.82674739</v>
+        <f>Data!I21*10^6</f>
+        <v>192108597.13120529</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
-    <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="79748b23-d81a-423e-9112-21109dc864e6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F92C12C-F9CE-4844-A9FE-92E1C70F48A9}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{637D4DA2-E71D-4E86-AF4A-596D7581519B}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1913C62-2019-4FBE-955D-B322DD85E640}"/>
 </file>